--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -10518,12 +10518,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10548,22 +10548,22 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -10596,40 +10596,185 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW69" t="inlineStr">
+      <c r="AW70" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
+      <c r="AX70" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr">
+      <c r="AY70" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
+      <c r="AZ70" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="BA69" t="inlineStr">
+      <c r="BA70" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB69" t="inlineStr">
+      <c r="BB70" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC69" t="inlineStr">
+      <c r="BC70" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -10751,7 +10896,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -10761,7 +10906,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -10813,7 +10958,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -9933,17 +9933,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -9977,56 +9977,138 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="n">
-        <v>1</v>
-      </c>
-      <c r="R65" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>143259</v>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SER_CN_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>SER_CN_VIRAL_HEPATITIS</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>SRC_CN_CDC</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>country:CN:national</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Source-reported aggregate; never derive it by summing subtype series.</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN65" t="b">
+        <v>0</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -10036,22 +10118,22 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -10113,7 +10195,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -10122,13 +10204,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -10258,7 +10340,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -10403,7 +10485,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -10412,13 +10494,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
-        <v>0.002450425222697299</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -10548,7 +10630,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -10557,13 +10639,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R69" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -10663,12 +10745,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10693,22 +10775,22 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -10741,40 +10823,185 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AW70" t="inlineStr">
+      <c r="AW71" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
+      <c r="AX71" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr">
+      <c r="AY71" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="BA70" t="inlineStr">
+      <c r="BA71" t="inlineStr">
         <is>
           <t>Australia NINDSS</t>
         </is>
       </c>
-      <c r="BB70" t="inlineStr">
+      <c r="BB71" t="inlineStr">
         <is>
           <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
-      <c r="BC70" t="inlineStr">
+      <c r="BC71" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -10906,7 +11133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -10926,7 +11153,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -11007,6 +11007,151 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11040,7 +11185,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11123,7 +11268,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -11133,7 +11278,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -7823,7 +7823,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -11147,6 +11147,151 @@
         </is>
       </c>
       <c r="BC72" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>2</v>
+      </c>
+      <c r="O73" t="n">
+        <v>2</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -11185,7 +11330,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11413,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -11278,7 +11423,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -11330,7 +11475,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -17653,6 +17653,151 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>2</v>
+      </c>
+      <c r="O102" t="n">
+        <v>2</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17686,7 +17831,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -17769,7 +17914,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -17779,7 +17924,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -17831,7 +17976,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1791,6 +1826,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1936,6 +1976,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2903,6 +2948,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3048,6 +3098,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3193,6 +3248,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3338,6 +3398,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3483,6 +3548,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3628,6 +3698,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3773,6 +3848,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3918,6 +3998,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4063,6 +4148,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5030,6 +5120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5175,6 +5270,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5320,6 +5420,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5465,6 +5570,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5610,6 +5720,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5755,6 +5870,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5900,6 +6020,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6045,6 +6170,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6190,6 +6320,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6927,6 +7062,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7072,6 +7212,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7217,6 +7362,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7362,6 +7512,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7507,6 +7662,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7652,6 +7812,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7797,6 +7962,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7942,6 +8112,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8087,6 +8262,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8824,6 +9004,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8969,6 +9154,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9114,6 +9304,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9259,6 +9454,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9404,6 +9604,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9549,6 +9754,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9694,6 +9904,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9839,6 +10054,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9984,6 +10204,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11323,6 +11548,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11468,6 +11698,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11613,6 +11848,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11758,6 +11998,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11903,6 +12148,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12048,6 +12298,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12193,6 +12448,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12338,6 +12598,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12483,6 +12748,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15024,6 +15294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15169,6 +15444,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15314,6 +15594,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15459,6 +15744,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15604,6 +15894,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15749,6 +16044,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15894,6 +16194,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16039,6 +16344,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16184,6 +16494,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19324,6 +19639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19469,6 +19789,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19614,6 +19939,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19759,6 +20089,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19904,6 +20239,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20049,6 +20389,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20194,6 +20539,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20339,6 +20689,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20484,6 +20839,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23170,6 +23530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23315,6 +23680,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23460,6 +23830,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23605,6 +23980,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23750,6 +24130,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23895,6 +24280,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24040,6 +24430,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24185,6 +24580,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24328,6 +24728,11 @@
       <c r="S147" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -25380,6 +25380,151 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>5</v>
+      </c>
+      <c r="O152" t="n">
+        <v>5</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25413,7 +25558,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -25496,7 +25641,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -25506,7 +25651,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -25558,7 +25703,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -1989,9 +1989,9 @@
       <c r="R11" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -2001,22 +2001,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2137,9 +2127,9 @@
       <c r="R12" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2149,22 +2139,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2285,9 +2265,9 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2297,22 +2277,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2433,9 +2403,9 @@
       <c r="R14" t="n">
         <v>0.004084042037828832</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2445,22 +2415,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -3799,9 +3759,9 @@
       <c r="R24" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3811,22 +3771,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -3947,9 +3897,9 @@
       <c r="R25" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3959,22 +3909,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4095,9 +4035,9 @@
       <c r="R26" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -4107,22 +4047,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4243,9 +4173,9 @@
       <c r="R27" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -4255,22 +4185,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -5609,9 +5529,9 @@
       <c r="R37" t="n">
         <v>0.004084042037828832</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5621,22 +5541,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5757,9 +5667,9 @@
       <c r="R38" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5769,22 +5679,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -5905,9 +5805,9 @@
       <c r="R39" t="n">
         <v>0.003267233630263065</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5917,22 +5817,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6053,9 +5943,9 @@
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -6065,22 +5955,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7416,9 +7296,9 @@
       <c r="R50" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -7428,22 +7308,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7564,9 +7434,9 @@
       <c r="R51" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -7576,22 +7446,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7712,9 +7572,9 @@
       <c r="R52" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7724,22 +7584,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -7860,9 +7710,9 @@
       <c r="R53" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7872,22 +7722,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -9223,9 +9063,9 @@
       <c r="R63" t="n">
         <v>0.003267233630263065</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -9235,22 +9075,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9371,9 +9201,9 @@
       <c r="R64" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -9383,22 +9213,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9519,9 +9339,9 @@
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -9531,22 +9351,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9667,9 +9477,9 @@
       <c r="R66" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -9679,22 +9489,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9815,9 +9615,9 @@
       <c r="R67" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -9827,22 +9627,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -11175,9 +10965,9 @@
       <c r="R77" t="n">
         <v>0.004900850445394598</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -11187,22 +10977,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11320,9 +11100,9 @@
       <c r="R78" t="n">
         <v>0.004900850445394598</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -11332,22 +11112,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11465,9 +11235,9 @@
       <c r="R79" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -11477,22 +11247,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11610,9 +11370,9 @@
       <c r="R80" t="n">
         <v>0.005717658852960364</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -11622,22 +11382,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12970,9 +12720,9 @@
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -12982,22 +12732,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13115,9 +12855,9 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -13127,22 +12867,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13260,9 +12990,9 @@
       <c r="R92" t="n">
         <v>0.004084042037828832</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -13272,22 +13002,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13405,9 +13125,9 @@
       <c r="R93" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -13417,22 +13137,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13550,9 +13260,9 @@
       <c r="R94" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -13562,22 +13272,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14910,9 +14610,9 @@
       <c r="R104" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -14922,22 +14622,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15055,9 +14745,9 @@
       <c r="R105" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -15067,22 +14757,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15200,9 +14880,9 @@
       <c r="R106" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -15212,22 +14892,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15345,9 +15015,9 @@
       <c r="R107" t="n">
         <v>0.002450425222697299</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -15357,22 +15027,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15490,9 +15150,9 @@
       <c r="R108" t="n">
         <v>0.0008168084075657662</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -15502,22 +15162,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -16850,9 +16500,9 @@
       <c r="R118" t="n">
         <v>0</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -16862,22 +16512,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -16995,9 +16635,9 @@
       <c r="R119" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -17007,22 +16647,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -17140,9 +16770,9 @@
       <c r="R120" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -17152,22 +16782,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -17285,9 +16905,9 @@
       <c r="R121" t="n">
         <v>0.001633616815131532</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -17297,22 +16917,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -17430,9 +17040,9 @@
       <c r="R122" t="n">
         <v>0.004084042037828832</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -17442,22 +17052,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -16993,12 +16993,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -17032,17 +17032,17 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0.004084042037828832</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -17061,40 +17061,175 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>viral-hepatitis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D006</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Viral Hepatitis</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>病毒性肝炎</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>5</v>
+      </c>
+      <c r="O123" t="n">
+        <v>5</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.004084042037828832</v>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW122" t="inlineStr">
+      <c r="AW123" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX122" t="inlineStr">
+      <c r="AX123" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY122" t="inlineStr">
+      <c r="AY123" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ122" t="inlineStr">
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA122" t="inlineStr">
+      <c r="BA123" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB122" t="inlineStr">
+      <c r="BB123" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC122" t="inlineStr">
+      <c r="BC123" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -17216,7 +17351,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
@@ -17226,7 +17361,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d006/2026-2029.xlsx
+++ b/diseases/d006/2026-2029.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -783,12 +788,22 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -906,6 +921,11 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -918,12 +938,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1041,6 +1071,11 @@
       <c r="R4" t="n">
         <v>0</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1053,12 +1088,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1176,6 +1221,11 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1188,12 +1238,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1311,6 +1371,11 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1323,12 +1388,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1446,6 +1521,11 @@
       <c r="R7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1458,12 +1538,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1581,6 +1671,11 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1593,12 +1688,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1716,6 +1821,11 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1728,12 +1838,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1851,6 +1971,11 @@
       <c r="R10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1863,12 +1988,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2541,6 +2676,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2553,12 +2693,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2676,6 +2826,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2688,12 +2843,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2811,6 +2976,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2823,12 +2993,22 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -2946,6 +3126,11 @@
       <c r="R18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2958,12 +3143,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3081,6 +3276,11 @@
       <c r="R19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3093,12 +3293,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3216,6 +3426,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3228,12 +3443,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3351,6 +3576,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3363,12 +3593,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3486,6 +3726,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3498,12 +3743,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3621,6 +3876,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3633,12 +3893,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4311,6 +4581,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4323,12 +4598,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4446,6 +4731,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4458,12 +4748,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4581,6 +4881,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4593,12 +4898,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4716,6 +5031,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4728,12 +5048,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -4851,6 +5181,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4863,12 +5198,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -4986,6 +5331,11 @@
       <c r="R33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4998,12 +5348,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5121,6 +5481,11 @@
       <c r="R34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5133,12 +5498,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5256,6 +5631,11 @@
       <c r="R35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5268,12 +5648,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5391,6 +5781,11 @@
       <c r="R36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5403,12 +5798,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6078,6 +6483,11 @@
       <c r="R41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6090,12 +6500,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6213,6 +6633,11 @@
       <c r="R42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6225,12 +6650,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6348,6 +6783,11 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6360,12 +6800,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6483,6 +6933,11 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6495,12 +6950,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6618,6 +7083,11 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6630,12 +7100,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -6753,6 +7233,11 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6765,12 +7250,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -6888,6 +7383,11 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6900,12 +7400,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7023,6 +7533,11 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7035,12 +7550,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7158,6 +7683,11 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7170,12 +7700,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7845,6 +8385,11 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7857,12 +8402,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -7980,6 +8535,11 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7992,12 +8552,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8115,6 +8685,11 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8127,12 +8702,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8250,6 +8835,11 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8262,12 +8852,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8385,6 +8985,11 @@
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8397,12 +9002,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8520,6 +9135,11 @@
       <c r="R59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8532,12 +9152,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8655,6 +9285,11 @@
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8667,12 +9302,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -8790,6 +9435,11 @@
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8802,12 +9452,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -8925,6 +9585,11 @@
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8937,12 +9602,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9750,6 +10425,11 @@
       <c r="R68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9762,12 +10442,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -9885,6 +10575,11 @@
       <c r="R69" t="n">
         <v>0</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9897,12 +10592,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10020,6 +10725,11 @@
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10032,12 +10742,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10155,6 +10875,11 @@
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10167,12 +10892,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10290,6 +11025,11 @@
       <c r="R72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10302,12 +11042,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10425,6 +11175,11 @@
       <c r="R73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10437,12 +11192,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -10560,6 +11325,11 @@
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10572,12 +11342,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -10695,6 +11475,11 @@
       <c r="R75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10707,12 +11492,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -10830,6 +11625,11 @@
       <c r="R76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10842,12 +11642,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11505,6 +12315,11 @@
       <c r="R81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11517,12 +12332,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -11640,6 +12465,11 @@
       <c r="R82" t="n">
         <v>0</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11652,12 +12482,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -11775,6 +12615,11 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11787,12 +12632,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -11910,6 +12765,11 @@
       <c r="R84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11922,12 +12782,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12045,6 +12915,11 @@
       <c r="R85" t="n">
         <v>0</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12057,12 +12932,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12180,6 +13065,11 @@
       <c r="R86" t="n">
         <v>0</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12192,12 +13082,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12315,6 +13215,11 @@
       <c r="R87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12327,12 +13232,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12450,6 +13365,11 @@
       <c r="R88" t="n">
         <v>0</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12462,12 +13382,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -12585,6 +13515,11 @@
       <c r="R89" t="n">
         <v>0</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12597,12 +13532,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13395,6 +14340,11 @@
       <c r="R95" t="n">
         <v>0</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13407,12 +14357,22 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -13530,6 +14490,11 @@
       <c r="R96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13542,12 +14507,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -13665,6 +14640,11 @@
       <c r="R97" t="n">
         <v>0</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13677,12 +14657,22 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -13800,6 +14790,11 @@
       <c r="R98" t="n">
         <v>0</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13812,12 +14807,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -13935,6 +14940,11 @@
       <c r="R99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13947,12 +14957,22 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14070,6 +15090,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14082,12 +15107,22 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14205,6 +15240,11 @@
       <c r="R101" t="n">
         <v>0</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14217,12 +15257,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14340,6 +15390,11 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14352,12 +15407,22 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -14475,6 +15540,11 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14487,12 +15557,22 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15285,6 +16365,11 @@
       <c r="R109" t="n">
         <v>0</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15297,12 +16382,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -15420,6 +16515,11 @@
       <c r="R110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15432,12 +16532,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -15555,6 +16665,11 @@
       <c r="R111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15567,12 +16682,22 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -15690,6 +16815,11 @@
       <c r="R112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15702,12 +16832,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -15825,6 +16965,11 @@
       <c r="R113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15837,12 +16982,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -15960,6 +17115,11 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15972,12 +17132,22 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -16095,6 +17265,11 @@
       <c r="R115" t="n">
         <v>0</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16107,12 +17282,22 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -16230,6 +17415,11 @@
       <c r="R116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16242,12 +17432,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -16365,6 +17565,11 @@
       <c r="R117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16377,12 +17582,22 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -17040,6 +18255,11 @@
       <c r="R122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17052,12 +18272,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
